--- a/5 Resources/Quality Assurance Testing Log.xlsx
+++ b/5 Resources/Quality Assurance Testing Log.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MAA2016-15 Supporting the Social Investment Unit\Exemplar project\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanas001\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2BD1BFC-807B-45F4-9743-B527603BAD08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testing guide" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="Detailed Testing" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Issues Log'!$B$7:$P$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Issues Log'!$B$7:$K$68</definedName>
     <definedName name="issue_10">#REF!</definedName>
     <definedName name="issue_11">#REF!</definedName>
     <definedName name="issue_12">#REF!</definedName>
@@ -31,151 +32,27 @@
     <definedName name="issue_26">#REF!</definedName>
     <definedName name="issue_4">#REF!</definedName>
     <definedName name="link_14">#REF!</definedName>
-    <definedName name="outcome">'Issues Log'!$N$2:$N$4</definedName>
+    <definedName name="outcome">'Issues Log'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Marianna Pekar</author>
-  </authors>
-  <commentList>
-    <comment ref="D3" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Marianna Pekar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-The review is considered done once all issues are closed. </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Marianna Pekar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This should describe why was the issue raised:
-(1) what happens currently when the code chunk is executed,
-(2) what should happen instead,
-(3) advice on how the issue could be resolved (optional) 
-(4) if it is a query, (2) and (3) should be replaced with a question and the reason why the quality of code chunk cannot be assessed (usually lack of documentation, undocumented assumptions)
- </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Marianna Pekar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Optional. Refer of the error types on the "testing guide" sheet </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Marianna Pekar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Link to relevant cell on the sheet "Detailed Testing". 
-Applicable if it aids developer understanding the issue. 
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Marianna Pekar:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-The developer's response on the issue, e.g. answering queries, confirming errors.  </t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>Practical Guidelines</t>
   </si>
@@ -504,36 +381,21 @@
     <t>Extensibility: how easy it is to update/customise the codes at a future date</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
     <t>Priority Key:</t>
   </si>
   <si>
     <t>Count</t>
   </si>
   <si>
-    <t>Outcome Key:</t>
-  </si>
-  <si>
     <t>Actual error, confirmed</t>
   </si>
   <si>
-    <t>Outstanding - developer to look at it</t>
-  </si>
-  <si>
     <t>Potential error, if inputs changed would result in actual error/High likelihood of misinterpretation</t>
   </si>
   <si>
-    <t>Outstanding - developer responded/code change - for reviewer</t>
-  </si>
-  <si>
     <t>Best practice</t>
   </si>
   <si>
-    <t>Closed</t>
-  </si>
-  <si>
     <t>Query</t>
   </si>
   <si>
@@ -564,22 +426,7 @@
     <t>Priority</t>
   </si>
   <si>
-    <t>Dev Feedback</t>
-  </si>
-  <si>
-    <t>Response Date</t>
-  </si>
-  <si>
-    <t>Outcome</t>
-  </si>
-  <si>
     <t>Comments</t>
-  </si>
-  <si>
-    <t>Date resolved</t>
-  </si>
-  <si>
-    <t>Developer</t>
   </si>
   <si>
     <t xml:space="preserve">Look at each line of the codes. Some lines deserve more scrutity than others, the reviewer needs to make a judgement call. </t>
@@ -626,15 +473,21 @@
   <si>
     <t>Line number</t>
   </si>
+  <si>
+    <t>Reviewed work:</t>
+  </si>
+  <si>
+    <t>Reviewed for:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -725,19 +578,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -796,19 +636,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="3"/>
-      </right>
-      <top style="thin">
-        <color theme="3"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="8"/>
       </left>
@@ -851,6 +678,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="3"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -867,9 +707,9 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="8"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -907,58 +747,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="9" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="7"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="9" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Accent1" xfId="7" builtinId="29"/>
     <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="Body Text" xfId="6"/>
-    <cellStyle name="Comma 2" xfId="10"/>
+    <cellStyle name="Body Text" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Comma 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Heading 1" xfId="1" builtinId="16" customBuiltin="1"/>
     <cellStyle name="Heading 2" xfId="2" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="3" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="4" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Heading 5" xfId="5"/>
+    <cellStyle name="Heading 5" xfId="5" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="9" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1115,30 +935,30 @@
     </dxf>
   </dxfs>
   <tableStyles count="7" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="SIA Table1 Teal" pivot="0" count="2">
+    <tableStyle name="SIA Table1 Teal" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="12"/>
       <tableStyleElement type="headerRow" dxfId="11"/>
     </tableStyle>
-    <tableStyle name="SIA Table2 Orange" pivot="0" count="2">
+    <tableStyle name="SIA Table2 Orange" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="10"/>
       <tableStyleElement type="headerRow" dxfId="9"/>
     </tableStyle>
-    <tableStyle name="SIA Table3 Purple" pivot="0" count="2">
+    <tableStyle name="SIA Table3 Purple" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="wholeTable" dxfId="8"/>
       <tableStyleElement type="headerRow" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="SIA Table4 Grey" pivot="0" count="1">
+    <tableStyle name="SIA Table4 Grey" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
     </tableStyle>
-    <tableStyle name="SIA Table5 Teal shaded" pivot="0" count="2">
+    <tableStyle name="SIA Table5 Teal shaded" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
       <tableStyleElement type="wholeTable" dxfId="5"/>
       <tableStyleElement type="firstColumn" dxfId="4"/>
     </tableStyle>
-    <tableStyle name="SIA Table6 Orange shaded" pivot="0" count="2">
+    <tableStyle name="SIA Table6 Orange shaded" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="firstColumn" dxfId="2"/>
     </tableStyle>
-    <tableStyle name="SIA Table7 Agenda items" pivot="0" count="2">
+    <tableStyle name="SIA Table7 Agenda items" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1386,9 +1206,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X51"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2.42578125" customWidth="1"/>
     <col min="3" max="3" width="3.7109375" customWidth="1"/>
@@ -1399,7 +1219,7 @@
     <col min="25" max="16384" width="9.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -1424,8 +1244,8 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23"/>
-    <row r="3" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C3" s="2">
         <v>1</v>
       </c>
@@ -1433,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C4" s="2">
         <f>C3+1</f>
         <v>2</v>
@@ -1442,16 +1262,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C5" s="2">
         <f>C4+1</f>
         <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C6" s="2">
         <f>C5+1</f>
         <v>4</v>
@@ -1460,7 +1280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C7" s="2">
         <f>C6+1</f>
         <v>5</v>
@@ -1469,7 +1289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="2">
@@ -1480,7 +1300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C9" s="2"/>
       <c r="D9" s="4" t="s">
         <v>6</v>
@@ -1489,7 +1309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C10" s="2"/>
       <c r="D10" s="5" t="s">
         <v>8</v>
@@ -1498,7 +1318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C11" s="2"/>
       <c r="D11" s="5" t="s">
         <v>10</v>
@@ -1507,7 +1327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C12" s="2">
         <f>C8+1</f>
         <v>7</v>
@@ -1516,7 +1336,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C13" s="2">
         <f>C12+1</f>
         <v>8</v>
@@ -1525,7 +1345,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C14" s="2">
         <f>C13+1</f>
         <v>9</v>
@@ -1534,7 +1354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C15" s="2">
         <f>C14+1</f>
         <v>10</v>
@@ -1543,7 +1363,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="C16" s="2">
         <f>C15+1</f>
         <v>11</v>
@@ -1552,7 +1372,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="3:23">
+    <row r="17" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C17" s="2">
         <f>C16+1</f>
         <v>12</v>
@@ -1561,7 +1381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="3:23">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C18" s="2">
         <v>13</v>
       </c>
@@ -1569,8 +1389,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="3:23"/>
-    <row r="20" spans="3:23">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.25">
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
         <v>19</v>
@@ -1595,10 +1415,10 @@
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
     </row>
-    <row r="21" spans="3:23">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="3:23">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D22" s="7" t="s">
         <v>20</v>
       </c>
@@ -1611,10 +1431,10 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
     </row>
-    <row r="23" spans="3:23">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D23" s="7"/>
       <c r="E23" s="8" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
@@ -1622,7 +1442,7 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
     </row>
-    <row r="24" spans="3:23" ht="45">
+    <row r="24" spans="3:23" ht="45" x14ac:dyDescent="0.25">
       <c r="D24" s="7" t="s">
         <v>22</v>
       </c>
@@ -1635,7 +1455,7 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
     </row>
-    <row r="25" spans="3:23">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D25" s="7"/>
       <c r="E25" s="8" t="s">
         <v>24</v>
@@ -1646,7 +1466,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
     </row>
-    <row r="26" spans="3:23">
+    <row r="26" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D26" s="7"/>
       <c r="E26" s="8" t="s">
         <v>25</v>
@@ -1657,7 +1477,7 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
     </row>
-    <row r="27" spans="3:23">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D27" s="7" t="s">
         <v>26</v>
       </c>
@@ -1670,7 +1490,7 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
     </row>
-    <row r="28" spans="3:23">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D28" s="7"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8" t="s">
@@ -1681,7 +1501,7 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
     </row>
-    <row r="29" spans="3:23">
+    <row r="29" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D29" s="7"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8" t="s">
@@ -1692,7 +1512,7 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
     </row>
-    <row r="30" spans="3:23">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D30" s="7" t="s">
         <v>30</v>
       </c>
@@ -1705,12 +1525,12 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
     </row>
-    <row r="31" spans="3:23">
+    <row r="31" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D31" s="7" t="s">
         <v>32</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
@@ -1718,7 +1538,7 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
     </row>
-    <row r="32" spans="3:23">
+    <row r="32" spans="3:23" x14ac:dyDescent="0.25">
       <c r="D32" s="7"/>
       <c r="E32" s="8" t="s">
         <v>33</v>
@@ -1729,7 +1549,7 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="4:10">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D33" s="7"/>
       <c r="E33" s="8" t="s">
         <v>34</v>
@@ -1740,34 +1560,37 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
     </row>
-    <row r="34" spans="4:10"/>
-    <row r="35" spans="4:10"/>
-    <row r="36" spans="4:10"/>
-    <row r="37" spans="4:10"/>
-    <row r="38" spans="4:10"/>
-    <row r="39" spans="4:10"/>
-    <row r="40" spans="4:10"/>
-    <row r="41" spans="4:10"/>
-    <row r="42" spans="4:10"/>
-    <row r="43" spans="4:10"/>
-    <row r="44" spans="4:10"/>
-    <row r="45" spans="4:10"/>
-    <row r="46" spans="4:10"/>
-    <row r="47" spans="4:10"/>
-    <row r="48" spans="4:10"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
+    <row r="34" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25"/>
+    <row r="49" x14ac:dyDescent="0.25"/>
+    <row r="50" x14ac:dyDescent="0.25"/>
+    <row r="51" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 IN-CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:P22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B1:M68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" customWidth="1"/>
@@ -1780,165 +1603,126 @@
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" customWidth="1"/>
     <col min="11" max="11" width="44.7109375" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
     <col min="13" max="13" width="11.5703125" customWidth="1"/>
-    <col min="14" max="15" width="32.7109375" customWidth="1"/>
-    <col min="16" max="16" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16">
-      <c r="C1" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="33"/>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C1" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="I1" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="J1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C2" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="22"/>
+      <c r="I2" s="15">
+        <v>1</v>
+      </c>
+      <c r="J2" s="16">
+        <f>COUNTIF(J$7:J$1048576,I2)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="M2" s="9"/>
+    </row>
+    <row r="3" spans="2:13" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="C3" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="22"/>
+      <c r="I3" s="17">
+        <v>2</v>
+      </c>
+      <c r="J3" s="18">
+        <f>COUNTIF(J$7:J$1048576,I3)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16">
-      <c r="C2" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="33"/>
-      <c r="J2" s="17">
-        <v>1</v>
-      </c>
-      <c r="K2" s="18" t="s">
+      <c r="M3" s="9"/>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C4" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="22"/>
+      <c r="I4" s="17">
+        <v>3</v>
+      </c>
+      <c r="J4" s="18">
+        <f>COUNTIF(J$7:J$1048576,I4)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="18">
-        <f>COUNTIF(J$7:J$1048576,J2)</f>
+      <c r="M4" s="9"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C5" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="I5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="18">
+        <f>COUNTIF(J$7:J$1048576,I5)</f>
         <v>0</v>
       </c>
-      <c r="M2" s="9"/>
-      <c r="N2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="O2" s="18">
-        <f>COUNTIF(N$7:N$1048576,N2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" ht="23.25">
-      <c r="C3" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" s="33"/>
-      <c r="J3" s="19">
-        <v>2</v>
-      </c>
-      <c r="K3" s="20" t="s">
+      <c r="K5" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="20">
-        <f>COUNTIF(J$7:J$1048576,J3)</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="9"/>
-      <c r="N3" s="19" t="s">
+      <c r="M5" s="9"/>
+    </row>
+    <row r="7" spans="2:13" s="3" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="20">
-        <f>COUNTIF(N$7:N$1048576,N3)</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="23"/>
-    </row>
-    <row r="4" spans="2:16">
-      <c r="J4" s="19">
-        <v>3</v>
-      </c>
-      <c r="K4" s="20" t="s">
+      <c r="C7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="20">
-        <f>COUNTIF(J$7:J$1048576,J4)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="19" t="s">
+      <c r="D7" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="O4" s="20">
-        <f>COUNTIF(N$7:N$1048576,N4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:16">
-      <c r="J5" s="19" t="s">
+      <c r="E7" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="G7" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="20">
-        <f>COUNTIF(J$7:J$1048576,J5)</f>
-        <v>0</v>
-      </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="19"/>
-    </row>
-    <row r="6" spans="2:16" s="23" customFormat="1"/>
-    <row r="7" spans="2:16" s="3" customFormat="1" ht="40.5" customHeight="1">
-      <c r="B7" s="10" t="s">
+      <c r="H7" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="I7" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="J7" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="K7" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="O7" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="P7" s="10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16">
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" s="11">
         <v>1</v>
       </c>
@@ -1947,17 +1731,12 @@
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="22"/>
+      <c r="H8" s="19"/>
       <c r="I8" s="13"/>
       <c r="J8" s="14"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="21"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="15"/>
-    </row>
-    <row r="9" spans="2:16">
+      <c r="K8" s="23"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="11">
         <v>2</v>
       </c>
@@ -1966,287 +1745,856 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="28"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="13"/>
       <c r="J9" s="14"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="15"/>
-    </row>
-    <row r="10" spans="2:16" s="23" customFormat="1">
-      <c r="B10" s="25">
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="11">
         <v>3</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="30"/>
-    </row>
-    <row r="11" spans="2:16" s="23" customFormat="1">
-      <c r="B11" s="25">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="11">
         <v>4</v>
       </c>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="30"/>
-    </row>
-    <row r="12" spans="2:16" s="23" customFormat="1">
-      <c r="B12" s="25">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="11">
         <v>5</v>
       </c>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="30"/>
-    </row>
-    <row r="13" spans="2:16" s="23" customFormat="1">
-      <c r="B13" s="25">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="23"/>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" s="11">
         <v>6</v>
       </c>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="30"/>
-    </row>
-    <row r="14" spans="2:16" s="23" customFormat="1">
-      <c r="B14" s="25">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="23"/>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="11">
         <v>7</v>
       </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="26"/>
-      <c r="O14" s="26"/>
-      <c r="P14" s="30"/>
-    </row>
-    <row r="15" spans="2:16" s="23" customFormat="1">
-      <c r="B15" s="25">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="23"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="11">
         <v>8</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="30"/>
-    </row>
-    <row r="16" spans="2:16" s="23" customFormat="1">
-      <c r="B16" s="25">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="11">
         <v>9</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="30"/>
-    </row>
-    <row r="17" spans="2:16" s="23" customFormat="1">
-      <c r="B17" s="25">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="23"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="11">
         <v>10</v>
       </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="26"/>
-      <c r="O17" s="26"/>
-      <c r="P17" s="30"/>
-    </row>
-    <row r="18" spans="2:16" s="23" customFormat="1">
-      <c r="B18" s="25">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="11">
         <v>11</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="30"/>
-    </row>
-    <row r="19" spans="2:16" s="23" customFormat="1">
-      <c r="B19" s="25">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="23"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="11">
         <v>12</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="30"/>
-    </row>
-    <row r="20" spans="2:16" s="23" customFormat="1">
-      <c r="B20" s="25">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="23"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="11">
         <v>13</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="30"/>
-    </row>
-    <row r="21" spans="2:16" s="23" customFormat="1">
-      <c r="B21" s="25">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="23"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="11">
         <v>14</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="26"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="26"/>
-      <c r="O21" s="26"/>
-      <c r="P21" s="30"/>
-    </row>
-    <row r="22" spans="2:16" s="23" customFormat="1">
-      <c r="B22" s="25">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="23"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="11">
         <v>15</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="26"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="26"/>
-      <c r="O22" s="26"/>
-      <c r="P22" s="30"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="11">
+        <v>16</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="23"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="11">
+        <v>17</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="23"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="11">
+        <v>18</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="23"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="11">
+        <v>19</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="23"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="11">
+        <v>20</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="23"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="11">
+        <v>21</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="13"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="23"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="11">
+        <v>22</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="23"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="11">
+        <v>23</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="23"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="11">
+        <v>24</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="23"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="11">
+        <v>25</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="23"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="11">
+        <v>26</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="23"/>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="11">
+        <v>27</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="23"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="11">
+        <v>28</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="23"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="11">
+        <v>29</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="23"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="11">
+        <v>30</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="23"/>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="11">
+        <v>31</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="23"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="11">
+        <v>32</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="23"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="11">
+        <v>33</v>
+      </c>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="23"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="11">
+        <v>34</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="23"/>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="11">
+        <v>35</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="23"/>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="11">
+        <v>36</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="21"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="23"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="11">
+        <v>37</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="23"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="11">
+        <v>38</v>
+      </c>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="23"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="11">
+        <v>39</v>
+      </c>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="23"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="11">
+        <v>40</v>
+      </c>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="23"/>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="11">
+        <v>41</v>
+      </c>
+      <c r="C48" s="12"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="21"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="23"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B49" s="11">
+        <v>42</v>
+      </c>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="12"/>
+      <c r="G49" s="12"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="23"/>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50" s="11">
+        <v>43</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="23"/>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B51" s="11">
+        <v>44</v>
+      </c>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="12"/>
+      <c r="H51" s="21"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="23"/>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B52" s="11">
+        <v>45</v>
+      </c>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="23"/>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="11">
+        <v>46</v>
+      </c>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="12"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="23"/>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B54" s="11">
+        <v>47</v>
+      </c>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="23"/>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B55" s="11">
+        <v>48</v>
+      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="23"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B56" s="11">
+        <v>49</v>
+      </c>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="12"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="11">
+        <v>50</v>
+      </c>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="23"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58" s="11">
+        <v>51</v>
+      </c>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="12"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="23"/>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B59" s="11">
+        <v>52</v>
+      </c>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="23"/>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="11">
+        <v>53</v>
+      </c>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="23"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61" s="11">
+        <v>54</v>
+      </c>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="23"/>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B62" s="11">
+        <v>55</v>
+      </c>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="23"/>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" s="11">
+        <v>56</v>
+      </c>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="12"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="23"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B64" s="11">
+        <v>57</v>
+      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="12"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="23"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B65" s="11">
+        <v>58</v>
+      </c>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="12"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="23"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" s="11">
+        <v>59</v>
+      </c>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="12"/>
+      <c r="H66" s="21"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="23"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B67" s="11">
+        <v>60</v>
+      </c>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="23"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B68" s="11">
+        <v>61</v>
+      </c>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="12"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="B7:P22">
-    <sortState ref="B9:R23">
-      <sortCondition ref="B8:B20"/>
-    </sortState>
-  </autoFilter>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8:J22">
-      <formula1>$J$2:$J$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N8:N22">
-      <formula1>outcome</formula1>
+  <autoFilter ref="B7:K68" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J8:J68" xr:uid="{00000000-0002-0000-0100-000000000000}">
+      <formula1>$I$2:$I$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 IN-CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:U2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B2:U2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -2255,33 +2603,35 @@
     <col min="17" max="17" width="35.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" s="23" customFormat="1"/>
-    <row r="2" spans="2:21">
-      <c r="B2" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
+    <row r="2" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B2" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 IN-CONFIDENCE&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>